--- a/artfynd/A 30987-2024 artfynd.xlsx
+++ b/artfynd/A 30987-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121291856</v>
+        <v>121291915</v>
       </c>
       <c r="B2" t="n">
-        <v>57348</v>
+        <v>90715</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>435850</v>
+        <v>435768</v>
       </c>
       <c r="R2" t="n">
-        <v>7008248</v>
+        <v>7008324</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-21</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121291859</v>
+        <v>121291916</v>
       </c>
       <c r="B3" t="n">
-        <v>57348</v>
+        <v>90715</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>435831</v>
+        <v>435816</v>
       </c>
       <c r="R3" t="n">
-        <v>7008374</v>
+        <v>7008410</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-21</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121291858</v>
+        <v>121291860</v>
       </c>
       <c r="B4" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>435854</v>
+        <v>435794</v>
       </c>
       <c r="R4" t="n">
-        <v>7008350</v>
+        <v>7008406</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +959,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121291914</v>
+        <v>121291858</v>
       </c>
       <c r="B5" t="n">
-        <v>90705</v>
+        <v>57351</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>435658</v>
+        <v>435854</v>
       </c>
       <c r="R5" t="n">
-        <v>7008233</v>
+        <v>7008350</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121291860</v>
+        <v>121291856</v>
       </c>
       <c r="B6" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>435794</v>
+        <v>435850</v>
       </c>
       <c r="R6" t="n">
-        <v>7008406</v>
+        <v>7008248</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1173,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121291916</v>
+        <v>121291857</v>
       </c>
       <c r="B7" t="n">
-        <v>90705</v>
+        <v>57351</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>435816</v>
+        <v>435989</v>
       </c>
       <c r="R7" t="n">
-        <v>7008410</v>
+        <v>7008326</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,6 +1276,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121291857</v>
+        <v>121291859</v>
       </c>
       <c r="B8" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>435989</v>
+        <v>435831</v>
       </c>
       <c r="R8" t="n">
-        <v>7008326</v>
+        <v>7008374</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121291915</v>
+        <v>121291914</v>
       </c>
       <c r="B9" t="n">
-        <v>90705</v>
+        <v>90715</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>435768</v>
+        <v>435658</v>
       </c>
       <c r="R9" t="n">
-        <v>7008324</v>
+        <v>7008233</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 30987-2024 artfynd.xlsx
+++ b/artfynd/A 30987-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121291915</v>
+        <v>121291859</v>
       </c>
       <c r="B2" t="n">
-        <v>90715</v>
+        <v>57351</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>435768</v>
+        <v>435831</v>
       </c>
       <c r="R2" t="n">
-        <v>7008324</v>
+        <v>7008374</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121291916</v>
+        <v>121291858</v>
       </c>
       <c r="B3" t="n">
-        <v>90715</v>
+        <v>57351</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>435816</v>
+        <v>435854</v>
       </c>
       <c r="R3" t="n">
-        <v>7008410</v>
+        <v>7008350</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -986,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121291858</v>
+        <v>121291915</v>
       </c>
       <c r="B5" t="n">
-        <v>57351</v>
+        <v>90715</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>435854</v>
+        <v>435768</v>
       </c>
       <c r="R5" t="n">
-        <v>7008350</v>
+        <v>7008324</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,11 +1072,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-21</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1307,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121291859</v>
+        <v>121291916</v>
       </c>
       <c r="B8" t="n">
-        <v>57351</v>
+        <v>90715</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>435831</v>
+        <v>435816</v>
       </c>
       <c r="R8" t="n">
-        <v>7008374</v>
+        <v>7008410</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,11 +1388,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-11-21</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 30987-2024 artfynd.xlsx
+++ b/artfynd/A 30987-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121291859</v>
+        <v>121291857</v>
       </c>
       <c r="B2" t="n">
         <v>57351</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>435831</v>
+        <v>435989</v>
       </c>
       <c r="R2" t="n">
-        <v>7008374</v>
+        <v>7008326</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121291858</v>
+        <v>121291856</v>
       </c>
       <c r="B3" t="n">
         <v>57351</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>435854</v>
+        <v>435850</v>
       </c>
       <c r="R3" t="n">
-        <v>7008350</v>
+        <v>7008248</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121291915</v>
+        <v>121291858</v>
       </c>
       <c r="B5" t="n">
-        <v>90715</v>
+        <v>57351</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>435768</v>
+        <v>435854</v>
       </c>
       <c r="R5" t="n">
-        <v>7008324</v>
+        <v>7008350</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,6 +1072,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121291856</v>
+        <v>121291915</v>
       </c>
       <c r="B6" t="n">
-        <v>57351</v>
+        <v>90727</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>435850</v>
+        <v>435768</v>
       </c>
       <c r="R6" t="n">
-        <v>7008248</v>
+        <v>7008324</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,11 +1179,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-21</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121291857</v>
+        <v>121291916</v>
       </c>
       <c r="B7" t="n">
-        <v>57351</v>
+        <v>90727</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>435989</v>
+        <v>435816</v>
       </c>
       <c r="R7" t="n">
-        <v>7008326</v>
+        <v>7008410</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,11 +1281,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-11-21</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121291916</v>
+        <v>121291859</v>
       </c>
       <c r="B8" t="n">
-        <v>90715</v>
+        <v>57351</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>435816</v>
+        <v>435831</v>
       </c>
       <c r="R8" t="n">
-        <v>7008410</v>
+        <v>7008374</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,6 +1383,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1417,7 +1417,7 @@
         <v>121291914</v>
       </c>
       <c r="B9" t="n">
-        <v>90715</v>
+        <v>90727</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 30987-2024 artfynd.xlsx
+++ b/artfynd/A 30987-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121291857</v>
+        <v>121291859</v>
       </c>
       <c r="B2" t="n">
         <v>57351</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>435989</v>
+        <v>435831</v>
       </c>
       <c r="R2" t="n">
-        <v>7008326</v>
+        <v>7008374</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121291860</v>
+        <v>121291915</v>
       </c>
       <c r="B4" t="n">
-        <v>57351</v>
+        <v>90728</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>435794</v>
+        <v>435768</v>
       </c>
       <c r="R4" t="n">
-        <v>7008406</v>
+        <v>7008324</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-21</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121291858</v>
+        <v>121291914</v>
       </c>
       <c r="B5" t="n">
-        <v>57351</v>
+        <v>90728</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>435854</v>
+        <v>435658</v>
       </c>
       <c r="R5" t="n">
-        <v>7008350</v>
+        <v>7008233</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-21</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121291915</v>
+        <v>121291858</v>
       </c>
       <c r="B6" t="n">
-        <v>90727</v>
+        <v>57351</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>435768</v>
+        <v>435854</v>
       </c>
       <c r="R6" t="n">
-        <v>7008324</v>
+        <v>7008350</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,6 +1169,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121291916</v>
+        <v>121291860</v>
       </c>
       <c r="B7" t="n">
-        <v>90727</v>
+        <v>57351</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>435816</v>
+        <v>435794</v>
       </c>
       <c r="R7" t="n">
-        <v>7008410</v>
+        <v>7008406</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,6 +1276,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,7 +1307,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121291859</v>
+        <v>121291857</v>
       </c>
       <c r="B8" t="n">
         <v>57351</v>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>435831</v>
+        <v>435989</v>
       </c>
       <c r="R8" t="n">
-        <v>7008374</v>
+        <v>7008326</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121291914</v>
+        <v>121291916</v>
       </c>
       <c r="B9" t="n">
-        <v>90727</v>
+        <v>90728</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>435658</v>
+        <v>435816</v>
       </c>
       <c r="R9" t="n">
-        <v>7008233</v>
+        <v>7008410</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 30987-2024 artfynd.xlsx
+++ b/artfynd/A 30987-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121291859</v>
+        <v>121291915</v>
       </c>
       <c r="B2" t="n">
-        <v>57351</v>
+        <v>90731</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>435831</v>
+        <v>435768</v>
       </c>
       <c r="R2" t="n">
-        <v>7008374</v>
+        <v>7008324</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-21</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121291856</v>
+        <v>121291859</v>
       </c>
       <c r="B3" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>435850</v>
+        <v>435831</v>
       </c>
       <c r="R3" t="n">
-        <v>7008248</v>
+        <v>7008374</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121291915</v>
+        <v>121291860</v>
       </c>
       <c r="B4" t="n">
-        <v>90728</v>
+        <v>57354</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>435768</v>
+        <v>435794</v>
       </c>
       <c r="R4" t="n">
-        <v>7008324</v>
+        <v>7008406</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,7 +994,7 @@
         <v>121291914</v>
       </c>
       <c r="B5" t="n">
-        <v>90728</v>
+        <v>90731</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>121291858</v>
       </c>
       <c r="B6" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121291860</v>
+        <v>121291916</v>
       </c>
       <c r="B7" t="n">
-        <v>57351</v>
+        <v>90731</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>435794</v>
+        <v>435816</v>
       </c>
       <c r="R7" t="n">
-        <v>7008406</v>
+        <v>7008410</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,11 +1276,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-11-21</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121291857</v>
+        <v>121291856</v>
       </c>
       <c r="B8" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>435989</v>
+        <v>435850</v>
       </c>
       <c r="R8" t="n">
-        <v>7008326</v>
+        <v>7008248</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121291916</v>
+        <v>121291857</v>
       </c>
       <c r="B9" t="n">
-        <v>90728</v>
+        <v>57354</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,21 +1425,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>435816</v>
+        <v>435989</v>
       </c>
       <c r="R9" t="n">
-        <v>7008410</v>
+        <v>7008326</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,6 +1485,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 30987-2024 artfynd.xlsx
+++ b/artfynd/A 30987-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121291915</v>
+        <v>121291856</v>
       </c>
       <c r="B2" t="n">
-        <v>90731</v>
+        <v>57354</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>435768</v>
+        <v>435850</v>
       </c>
       <c r="R2" t="n">
-        <v>7008324</v>
+        <v>7008248</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121291859</v>
+        <v>121291916</v>
       </c>
       <c r="B3" t="n">
-        <v>57354</v>
+        <v>90731</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>435831</v>
+        <v>435816</v>
       </c>
       <c r="R3" t="n">
-        <v>7008374</v>
+        <v>7008410</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-21</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121291860</v>
+        <v>121291915</v>
       </c>
       <c r="B4" t="n">
-        <v>57354</v>
+        <v>90731</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>435794</v>
+        <v>435768</v>
       </c>
       <c r="R4" t="n">
-        <v>7008406</v>
+        <v>7008324</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-21</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121291914</v>
+        <v>121291858</v>
       </c>
       <c r="B5" t="n">
-        <v>90731</v>
+        <v>57354</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>435658</v>
+        <v>435854</v>
       </c>
       <c r="R5" t="n">
-        <v>7008233</v>
+        <v>7008350</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121291858</v>
+        <v>121291857</v>
       </c>
       <c r="B6" t="n">
         <v>57354</v>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>435854</v>
+        <v>435989</v>
       </c>
       <c r="R6" t="n">
-        <v>7008350</v>
+        <v>7008326</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121291916</v>
+        <v>121291860</v>
       </c>
       <c r="B7" t="n">
-        <v>90731</v>
+        <v>57354</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>435816</v>
+        <v>435794</v>
       </c>
       <c r="R7" t="n">
-        <v>7008410</v>
+        <v>7008406</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,6 +1276,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121291856</v>
+        <v>121291914</v>
       </c>
       <c r="B8" t="n">
-        <v>57354</v>
+        <v>90731</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>435850</v>
+        <v>435658</v>
       </c>
       <c r="R8" t="n">
-        <v>7008248</v>
+        <v>7008233</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1378,11 +1383,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-11-21</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,7 +1409,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121291857</v>
+        <v>121291859</v>
       </c>
       <c r="B9" t="n">
         <v>57354</v>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>435989</v>
+        <v>435831</v>
       </c>
       <c r="R9" t="n">
-        <v>7008326</v>
+        <v>7008374</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 30987-2024 artfynd.xlsx
+++ b/artfynd/A 30987-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121291856</v>
+        <v>121291915</v>
       </c>
       <c r="B2" t="n">
-        <v>57354</v>
+        <v>90737</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>435850</v>
+        <v>435768</v>
       </c>
       <c r="R2" t="n">
-        <v>7008248</v>
+        <v>7008324</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-21</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121291916</v>
+        <v>121291856</v>
       </c>
       <c r="B3" t="n">
-        <v>90731</v>
+        <v>57355</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>435816</v>
+        <v>435850</v>
       </c>
       <c r="R3" t="n">
-        <v>7008410</v>
+        <v>7008248</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121291915</v>
+        <v>121291914</v>
       </c>
       <c r="B4" t="n">
-        <v>90731</v>
+        <v>90737</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>435768</v>
+        <v>435658</v>
       </c>
       <c r="R4" t="n">
-        <v>7008324</v>
+        <v>7008233</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121291858</v>
+        <v>121291916</v>
       </c>
       <c r="B5" t="n">
-        <v>57354</v>
+        <v>90737</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>435854</v>
+        <v>435816</v>
       </c>
       <c r="R5" t="n">
-        <v>7008350</v>
+        <v>7008410</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,11 +1062,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-21</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121291857</v>
+        <v>121291858</v>
       </c>
       <c r="B6" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>435989</v>
+        <v>435854</v>
       </c>
       <c r="R6" t="n">
-        <v>7008326</v>
+        <v>7008350</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1168,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1203,7 +1198,7 @@
         <v>121291860</v>
       </c>
       <c r="B7" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1307,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121291914</v>
+        <v>121291857</v>
       </c>
       <c r="B8" t="n">
-        <v>90731</v>
+        <v>57355</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>435658</v>
+        <v>435989</v>
       </c>
       <c r="R8" t="n">
-        <v>7008233</v>
+        <v>7008326</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,6 +1378,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1412,7 +1412,7 @@
         <v>121291859</v>
       </c>
       <c r="B9" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 30987-2024 artfynd.xlsx
+++ b/artfynd/A 30987-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121291915</v>
       </c>
       <c r="B2" t="n">
-        <v>90737</v>
+        <v>90738</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121291856</v>
+        <v>121291857</v>
       </c>
       <c r="B3" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>435850</v>
+        <v>435989</v>
       </c>
       <c r="R3" t="n">
-        <v>7008248</v>
+        <v>7008326</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121291914</v>
+        <v>121291916</v>
       </c>
       <c r="B4" t="n">
-        <v>90737</v>
+        <v>90738</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>435658</v>
+        <v>435816</v>
       </c>
       <c r="R4" t="n">
-        <v>7008233</v>
+        <v>7008410</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121291916</v>
+        <v>121291859</v>
       </c>
       <c r="B5" t="n">
-        <v>90737</v>
+        <v>57356</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>435816</v>
+        <v>435831</v>
       </c>
       <c r="R5" t="n">
-        <v>7008410</v>
+        <v>7008374</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121291858</v>
+        <v>121291860</v>
       </c>
       <c r="B6" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1128,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>435854</v>
+        <v>435794</v>
       </c>
       <c r="R6" t="n">
-        <v>7008350</v>
+        <v>7008406</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1173,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121291860</v>
+        <v>121291914</v>
       </c>
       <c r="B7" t="n">
-        <v>57355</v>
+        <v>90738</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>435794</v>
+        <v>435658</v>
       </c>
       <c r="R7" t="n">
-        <v>7008406</v>
+        <v>7008233</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,11 +1276,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-11-21</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121291857</v>
+        <v>121291856</v>
       </c>
       <c r="B8" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>435989</v>
+        <v>435850</v>
       </c>
       <c r="R8" t="n">
-        <v>7008326</v>
+        <v>7008248</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121291859</v>
+        <v>121291858</v>
       </c>
       <c r="B9" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>435831</v>
+        <v>435854</v>
       </c>
       <c r="R9" t="n">
-        <v>7008374</v>
+        <v>7008350</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 30987-2024 artfynd.xlsx
+++ b/artfynd/A 30987-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121291915</v>
+        <v>121291857</v>
       </c>
       <c r="B2" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>435768</v>
+        <v>435989</v>
       </c>
       <c r="R2" t="n">
-        <v>7008324</v>
+        <v>7008326</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121291857</v>
+        <v>121291856</v>
       </c>
       <c r="B3" t="n">
         <v>57356</v>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>435989</v>
+        <v>435850</v>
       </c>
       <c r="R3" t="n">
-        <v>7008326</v>
+        <v>7008248</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121291916</v>
+        <v>121291859</v>
       </c>
       <c r="B4" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>435816</v>
+        <v>435831</v>
       </c>
       <c r="R4" t="n">
-        <v>7008410</v>
+        <v>7008374</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121291859</v>
+        <v>121291860</v>
       </c>
       <c r="B5" t="n">
         <v>57356</v>
@@ -1026,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>435831</v>
+        <v>435794</v>
       </c>
       <c r="R5" t="n">
-        <v>7008374</v>
+        <v>7008406</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121291860</v>
+        <v>121291916</v>
       </c>
       <c r="B6" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>435794</v>
+        <v>435816</v>
       </c>
       <c r="R6" t="n">
-        <v>7008406</v>
+        <v>7008410</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,11 +1179,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-21</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121291914</v>
+        <v>121291915</v>
       </c>
       <c r="B7" t="n">
         <v>90738</v>
@@ -1240,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>435658</v>
+        <v>435768</v>
       </c>
       <c r="R7" t="n">
-        <v>7008233</v>
+        <v>7008324</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121291856</v>
+        <v>121291914</v>
       </c>
       <c r="B8" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>435850</v>
+        <v>435658</v>
       </c>
       <c r="R8" t="n">
-        <v>7008248</v>
+        <v>7008233</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1378,11 +1383,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-11-21</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 30987-2024 artfynd.xlsx
+++ b/artfynd/A 30987-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121291857</v>
+        <v>121291859</v>
       </c>
       <c r="B2" t="n">
         <v>57356</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>435989</v>
+        <v>435831</v>
       </c>
       <c r="R2" t="n">
-        <v>7008326</v>
+        <v>7008374</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121291859</v>
+        <v>121291858</v>
       </c>
       <c r="B4" t="n">
         <v>57356</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>435831</v>
+        <v>435854</v>
       </c>
       <c r="R4" t="n">
-        <v>7008374</v>
+        <v>7008350</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121291860</v>
+        <v>121291857</v>
       </c>
       <c r="B5" t="n">
         <v>57356</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>435794</v>
+        <v>435989</v>
       </c>
       <c r="R5" t="n">
-        <v>7008406</v>
+        <v>7008326</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1409,7 +1409,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121291858</v>
+        <v>121291860</v>
       </c>
       <c r="B9" t="n">
         <v>57356</v>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>435854</v>
+        <v>435794</v>
       </c>
       <c r="R9" t="n">
-        <v>7008350</v>
+        <v>7008406</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 30987-2024 artfynd.xlsx
+++ b/artfynd/A 30987-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121291859</v>
+        <v>121291914</v>
       </c>
       <c r="B2" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>435831</v>
+        <v>435658</v>
       </c>
       <c r="R2" t="n">
-        <v>7008374</v>
+        <v>7008233</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-21</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121291856</v>
+        <v>121291857</v>
       </c>
       <c r="B3" t="n">
         <v>57356</v>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>435850</v>
+        <v>435989</v>
       </c>
       <c r="R3" t="n">
-        <v>7008248</v>
+        <v>7008326</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121291858</v>
+        <v>121291856</v>
       </c>
       <c r="B4" t="n">
         <v>57356</v>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>435854</v>
+        <v>435850</v>
       </c>
       <c r="R4" t="n">
-        <v>7008350</v>
+        <v>7008248</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +964,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121291857</v>
+        <v>121291860</v>
       </c>
       <c r="B5" t="n">
         <v>57356</v>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>435989</v>
+        <v>435794</v>
       </c>
       <c r="R5" t="n">
-        <v>7008326</v>
+        <v>7008406</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1307,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121291914</v>
+        <v>121291858</v>
       </c>
       <c r="B8" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>435658</v>
+        <v>435854</v>
       </c>
       <c r="R8" t="n">
-        <v>7008233</v>
+        <v>7008350</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,6 +1378,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,7 +1409,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121291860</v>
+        <v>121291859</v>
       </c>
       <c r="B9" t="n">
         <v>57356</v>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>435794</v>
+        <v>435831</v>
       </c>
       <c r="R9" t="n">
-        <v>7008406</v>
+        <v>7008374</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 30987-2024 artfynd.xlsx
+++ b/artfynd/A 30987-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121291914</v>
       </c>
       <c r="B2" t="n">
-        <v>90738</v>
+        <v>90743</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121291857</v>
+        <v>121291859</v>
       </c>
       <c r="B3" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>435989</v>
+        <v>435831</v>
       </c>
       <c r="R3" t="n">
-        <v>7008326</v>
+        <v>7008374</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
         <v>121291856</v>
       </c>
       <c r="B4" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121291860</v>
+        <v>121291858</v>
       </c>
       <c r="B5" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>435794</v>
+        <v>435854</v>
       </c>
       <c r="R5" t="n">
-        <v>7008406</v>
+        <v>7008350</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121291916</v>
+        <v>121291915</v>
       </c>
       <c r="B6" t="n">
-        <v>90738</v>
+        <v>90743</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>435816</v>
+        <v>435768</v>
       </c>
       <c r="R6" t="n">
-        <v>7008410</v>
+        <v>7008324</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121291915</v>
+        <v>121291857</v>
       </c>
       <c r="B7" t="n">
-        <v>90738</v>
+        <v>57357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>435768</v>
+        <v>435989</v>
       </c>
       <c r="R7" t="n">
-        <v>7008324</v>
+        <v>7008326</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,6 +1276,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121291858</v>
+        <v>121291860</v>
       </c>
       <c r="B8" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1342,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>435854</v>
+        <v>435794</v>
       </c>
       <c r="R8" t="n">
-        <v>7008350</v>
+        <v>7008406</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,7 +1387,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121291859</v>
+        <v>121291916</v>
       </c>
       <c r="B9" t="n">
-        <v>57356</v>
+        <v>90743</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,21 +1430,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>435831</v>
+        <v>435816</v>
       </c>
       <c r="R9" t="n">
-        <v>7008374</v>
+        <v>7008410</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,11 +1490,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-11-21</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
